--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0193.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0193.xlsx
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta hiểu ý ngươi.</t>
+          <t>Tao hiểu ý mày.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ta hiểu ý ngươi.</t>
+          <t>Tao hiểu ý mày.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Ta hiểu ý ngươi.</t>
+          <t>Tao hiểu ý mày.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ta hiểu ý ngươi.</t>
+          <t>Tao hiểu ý mày.</t>
         </is>
       </c>
     </row>
